--- a/models/users.xlsx
+++ b/models/users.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F55455A-3D2A-5A41-9666-4B6C581EFEAD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0247217-AEE3-1742-BDC4-1E8CBEAA6A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22620" yWindow="14000" windowWidth="33600" windowHeight="18800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
   <si>
     <t>name</t>
   </si>
@@ -381,6 +381,18 @@
   </si>
   <si>
     <t>orgname</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>user-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>superuser</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -493,7 +505,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -532,6 +544,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1187,11 +1202,19 @@
         <v>96</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="23">
-      <c r="C2" s="11"/>
+      <c r="A2" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="3" spans="1:3" ht="23">
       <c r="C3" s="11"/>

--- a/models/users.xlsx
+++ b/models/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0247217-AEE3-1742-BDC4-1E8CBEAA6A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7881A82-1017-9442-BE08-536B3BADD052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22620" yWindow="14000" windowWidth="33600" windowHeight="18800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="4060" windowWidth="33600" windowHeight="18800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>

--- a/models/users.xlsx
+++ b/models/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7881A82-1017-9442-BE08-536B3BADD052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC07DA42-6D63-AD4D-8220-BE2A61B64F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="4060" windowWidth="33600" windowHeight="18800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="4060" windowWidth="33600" windowHeight="18800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="111">
   <si>
     <t>name</t>
   </si>
@@ -393,6 +393,14 @@
   </si>
   <si>
     <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>idx2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique:username</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -542,11 +550,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1092,6 +1100,17 @@
         <v>82</v>
       </c>
     </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="5" spans="1:3">
       <c r="C5" s="5"/>
     </row>
@@ -1212,7 +1231,7 @@
       <c r="B2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1549,14 +1568,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="12"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
